--- a/reports/raw-views/assets/tables/meso_category_usage_frequency_agents.xlsx
+++ b/reports/raw-views/assets/tables/meso_category_usage_frequency_agents.xlsx
@@ -425,33 +425,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>label</t>
+          <t>level</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Autores</t>
+          <t>Authors Score 1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Pares</t>
+          <t>Authors Score 3</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Analistas</t>
+          <t>Authors Score 5</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Peers</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Analysts SV</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Analysts VS</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>AI ChatGPT</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>AI Gemini</t>
         </is>
       </c>
     </row>
@@ -462,73 +482,121 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>154</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
+        <v>49</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E2" t="n">
         <v>590</v>
       </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>saúde</t>
+          <t>maternidade</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
         <v>4</v>
       </c>
-      <c r="E3" t="n">
+      <c r="I3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>sistema penitenciário</t>
+          <t>saúde</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>61</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>nacionalidade e nacionalismo</t>
+          <t>sistema penitenciário</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -538,206 +606,338 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
         <v>79</v>
       </c>
-      <c r="D6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>amizade</t>
+          <t>recreação, lazer e entretenimento</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>462</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pessoas com deficiência</t>
+          <t>amizade</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>23</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>3</v>
       </c>
-      <c r="E8" t="n">
-        <v>3</v>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>maternidade</t>
+          <t>nacionalidade e nacionalismo</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>66</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>raça e racismo</t>
+          <t>linguagem e representação</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>26</v>
+      </c>
+      <c r="D10" t="n">
+        <v>13</v>
+      </c>
+      <c r="E10" t="n">
+        <v>240</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" t="n">
         <v>3</v>
       </c>
-      <c r="C10" t="n">
-        <v>23</v>
-      </c>
-      <c r="D10" t="n">
-        <v>6</v>
-      </c>
-      <c r="E10" t="n">
-        <v>4</v>
+      <c r="I10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>sociedade e consumo</t>
+          <t>pessoas com deficiência</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>202</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>linguagem e representação</t>
+          <t>questão agrária e territorial</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>240</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>127</v>
+      </c>
+      <c r="F12" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>violência</t>
+          <t>tecnologia, inovação e sociedade</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
+        <v>114</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>9</v>
+      </c>
+      <c r="H13" t="n">
         <v>5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>recreação, lazer e entretenimento</t>
+          <t>sociedade e consumo</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>462</v>
+        <v>23</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>202</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>família</t>
+          <t>moradia e habitação</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>162</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
+        <v>18</v>
+      </c>
+      <c r="F15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G15" t="n">
+        <v>10</v>
+      </c>
+      <c r="H15" t="n">
         <v>6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>sonho e fantasia</t>
+          <t>família</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>162</v>
+      </c>
+      <c r="F16" t="n">
+        <v>34</v>
+      </c>
+      <c r="G16" t="n">
+        <v>10</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -747,92 +947,152 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" t="n">
+        <v>9</v>
+      </c>
+      <c r="E17" t="n">
         <v>134</v>
       </c>
-      <c r="D17" t="n">
-        <v>7</v>
-      </c>
-      <c r="E17" t="n">
-        <v>7</v>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>distopia, ficção científica e futuros imaginados</t>
+          <t>violência</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>7</v>
+        <v>96</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>tecnologia, inovação e sociedade</t>
+          <t>sonho e fantasia</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>114</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>22</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>questão agrária e territorial</t>
+          <t>sonoridade e paisagem sonora</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>127</v>
+        <v>12</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E20" t="n">
-        <v>8</v>
+        <v>140</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G20" t="n">
+        <v>7</v>
+      </c>
+      <c r="H20" t="n">
+        <v>10</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>moradia e habitação</t>
+          <t>raça e racismo</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>8</v>
+        <v>23</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -842,54 +1102,90 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
+        <v>12</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
         <v>102</v>
       </c>
-      <c r="D22" t="n">
-        <v>21</v>
-      </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
+        <v>11</v>
+      </c>
+      <c r="G22" t="n">
         <v>10</v>
+      </c>
+      <c r="H22" t="n">
+        <v>5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>territorialidade e colonialismo</t>
+          <t>distopia, ficção científica e futuros imaginados</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E23" t="n">
-        <v>11</v>
+        <v>121</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>violências e preconceitos de gênero</t>
+          <t>gênero e sexualidade</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="D24" t="n">
+        <v>9</v>
+      </c>
+      <c r="E24" t="n">
+        <v>322</v>
+      </c>
+      <c r="F24" t="n">
         <v>4</v>
       </c>
-      <c r="E24" t="n">
-        <v>12</v>
+      <c r="G24" t="n">
+        <v>6</v>
+      </c>
+      <c r="H24" t="n">
+        <v>8</v>
+      </c>
+      <c r="I24" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="25">
@@ -899,54 +1195,90 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
+        <v>14</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
         <v>116</v>
       </c>
-      <c r="D25" t="n">
-        <v>8</v>
-      </c>
-      <c r="E25" t="n">
-        <v>13</v>
+      <c r="F25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>6</v>
+      </c>
+      <c r="I25" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>sonoridade e paisagem sonora</t>
+          <t>religião, espiritualidade e cosmologias</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>140</v>
+        <v>11</v>
       </c>
       <c r="D26" t="n">
+        <v>7</v>
+      </c>
+      <c r="E26" t="n">
+        <v>124</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6</v>
+      </c>
+      <c r="G26" t="n">
+        <v>8</v>
+      </c>
+      <c r="H26" t="n">
         <v>11</v>
       </c>
-      <c r="E26" t="n">
-        <v>14</v>
+      <c r="I26" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>gênero e sexualidade</t>
+          <t>trabalho e ofício</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>322</v>
+        <v>25</v>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E27" t="n">
+        <v>286</v>
+      </c>
+      <c r="F27" t="n">
         <v>14</v>
+      </c>
+      <c r="G27" t="n">
+        <v>15</v>
+      </c>
+      <c r="H27" t="n">
+        <v>8</v>
+      </c>
+      <c r="I27" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="28">
@@ -956,358 +1288,586 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
         <v>25</v>
       </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>15</v>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>6</v>
+      </c>
+      <c r="I28" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>trabalho e ofício</t>
+          <t>corpo, performance e expressão</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>86</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>286</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="E29" t="n">
-        <v>16</v>
+        <v>156</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" t="n">
+        <v>18</v>
+      </c>
+      <c r="I29" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>direitos humanos</t>
+          <t>crises e desastres ambientais e sociais</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>86</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" t="n">
         <v>9</v>
       </c>
-      <c r="E30" t="n">
-        <v>17</v>
+      <c r="H30" t="n">
+        <v>8</v>
+      </c>
+      <c r="I30" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>crises e desastres ambientais e sociais</t>
+          <t>territorialidade e colonialismo</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
+        <v>15</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
         <v>86</v>
       </c>
-      <c r="D31" t="n">
-        <v>14</v>
-      </c>
-      <c r="E31" t="n">
-        <v>17</v>
+      <c r="F31" t="n">
+        <v>7</v>
+      </c>
+      <c r="G31" t="n">
+        <v>9</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>religião, espiritualidade e cosmologias</t>
+          <t>saudade, luto ou perda</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>124</v>
+        <v>17</v>
       </c>
       <c r="D32" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>19</v>
+        <v>110</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>6</v>
+      </c>
+      <c r="H32" t="n">
+        <v>10</v>
+      </c>
+      <c r="I32" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>solidão</t>
+          <t>estruturas sociais e econômicas</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="D33" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E33" t="n">
-        <v>19</v>
+        <v>520</v>
+      </c>
+      <c r="F33" t="n">
+        <v>13</v>
+      </c>
+      <c r="G33" t="n">
+        <v>10</v>
+      </c>
+      <c r="H33" t="n">
+        <v>16</v>
+      </c>
+      <c r="I33" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>saudade, luto ou perda</t>
+          <t>violências e preconceitos de gênero</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>110</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>20</v>
+        <v>70</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>política</t>
+          <t>memória e patrimônio</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>380</v>
+        <v>44</v>
       </c>
       <c r="D35" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>23</v>
+        <v>379</v>
+      </c>
+      <c r="F35" t="n">
+        <v>11</v>
+      </c>
+      <c r="G35" t="n">
+        <v>14</v>
+      </c>
+      <c r="H35" t="n">
+        <v>16</v>
+      </c>
+      <c r="I35" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>dinâmica urbana</t>
+          <t>direitos humanos</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>427</v>
+        <v>11</v>
       </c>
       <c r="D36" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>23</v>
+        <v>88</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>8</v>
+      </c>
+      <c r="H36" t="n">
+        <v>6</v>
+      </c>
+      <c r="I36" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>vida afetiva</t>
+          <t>dinâmica urbana</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>313</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>1001</v>
+        <v>61</v>
       </c>
       <c r="D37" t="n">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="E37" t="n">
-        <v>25</v>
+        <v>427</v>
+      </c>
+      <c r="F37" t="n">
+        <v>27</v>
+      </c>
+      <c r="G37" t="n">
+        <v>21</v>
+      </c>
+      <c r="H37" t="n">
+        <v>11</v>
+      </c>
+      <c r="I37" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>estruturas sociais e econômicas</t>
+          <t>cultural</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>159</v>
+        <v>4</v>
       </c>
       <c r="C38" t="n">
-        <v>520</v>
+        <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E38" t="n">
+        <v>660</v>
+      </c>
+      <c r="F38" t="n">
         <v>26</v>
+      </c>
+      <c r="G38" t="n">
+        <v>17</v>
+      </c>
+      <c r="H38" t="n">
+        <v>14</v>
+      </c>
+      <c r="I38" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>educação e socialização</t>
+          <t>vida afetiva</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>104</v>
+        <v>3</v>
       </c>
       <c r="C39" t="n">
-        <v>312</v>
+        <v>102</v>
       </c>
       <c r="D39" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="E39" t="n">
-        <v>26</v>
+        <v>1001</v>
+      </c>
+      <c r="F39" t="n">
+        <v>29</v>
+      </c>
+      <c r="G39" t="n">
+        <v>30</v>
+      </c>
+      <c r="H39" t="n">
+        <v>12</v>
+      </c>
+      <c r="I39" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>cultural</t>
+          <t>pandemia</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>196</v>
+        <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>660</v>
+        <v>16</v>
       </c>
       <c r="D40" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E40" t="n">
-        <v>27</v>
+        <v>304</v>
+      </c>
+      <c r="F40" t="n">
+        <v>23</v>
+      </c>
+      <c r="G40" t="n">
+        <v>25</v>
+      </c>
+      <c r="H40" t="n">
+        <v>16</v>
+      </c>
+      <c r="I40" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>corpo, performance e expressão</t>
+          <t>povos originários e comunidades tradicionais</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>156</v>
+        <v>32</v>
       </c>
       <c r="D41" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E41" t="n">
-        <v>27</v>
+        <v>228</v>
+      </c>
+      <c r="F41" t="n">
+        <v>9</v>
+      </c>
+      <c r="G41" t="n">
+        <v>10</v>
+      </c>
+      <c r="H41" t="n">
+        <v>16</v>
+      </c>
+      <c r="I41" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>memória e patrimônio</t>
+          <t>solidão</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>379</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
         <v>27</v>
       </c>
+      <c r="F42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G42" t="n">
+        <v>8</v>
+      </c>
+      <c r="H42" t="n">
+        <v>6</v>
+      </c>
+      <c r="I42" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>povos originários e comunidades tradicionais</t>
+          <t>mulher, feminino e feminismo</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>228</v>
+        <v>5</v>
       </c>
       <c r="D43" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E43" t="n">
-        <v>29</v>
+        <v>61</v>
+      </c>
+      <c r="F43" t="n">
+        <v>10</v>
+      </c>
+      <c r="G43" t="n">
+        <v>12</v>
+      </c>
+      <c r="H43" t="n">
+        <v>17</v>
+      </c>
+      <c r="I43" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>pandemia</t>
+          <t>vida cotidiana</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>304</v>
+        <v>10</v>
       </c>
       <c r="D44" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>29</v>
+        <v>107</v>
+      </c>
+      <c r="F44" t="n">
+        <v>9</v>
+      </c>
+      <c r="G44" t="n">
+        <v>9</v>
+      </c>
+      <c r="H44" t="n">
+        <v>23</v>
+      </c>
+      <c r="I44" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>mulher, feminino e feminismo</t>
+          <t>educação e socialização</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="D45" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E45" t="n">
-        <v>31</v>
+        <v>312</v>
+      </c>
+      <c r="F45" t="n">
+        <v>15</v>
+      </c>
+      <c r="G45" t="n">
+        <v>11</v>
+      </c>
+      <c r="H45" t="n">
+        <v>11</v>
+      </c>
+      <c r="I45" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>vida cotidiana</t>
+          <t>política</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>107</v>
+        <v>33</v>
       </c>
       <c r="D46" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E46" t="n">
-        <v>37</v>
+        <v>380</v>
+      </c>
+      <c r="F46" t="n">
+        <v>17</v>
+      </c>
+      <c r="G46" t="n">
+        <v>12</v>
+      </c>
+      <c r="H46" t="n">
+        <v>7</v>
+      </c>
+      <c r="I46" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="47">
@@ -1317,54 +1877,90 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C47" t="n">
+        <v>9</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
         <v>80</v>
       </c>
-      <c r="D47" t="n">
-        <v>27</v>
-      </c>
-      <c r="E47" t="n">
-        <v>37</v>
+      <c r="F47" t="n">
+        <v>10</v>
+      </c>
+      <c r="G47" t="n">
+        <v>17</v>
+      </c>
+      <c r="H47" t="n">
+        <v>17</v>
+      </c>
+      <c r="I47" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>saúde mental</t>
+          <t>ambiental</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>106</v>
+        <v>4</v>
       </c>
       <c r="C48" t="n">
-        <v>284</v>
+        <v>49</v>
       </c>
       <c r="D48" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>39</v>
+        <v>346</v>
+      </c>
+      <c r="F48" t="n">
+        <v>31</v>
+      </c>
+      <c r="G48" t="n">
+        <v>21</v>
+      </c>
+      <c r="H48" t="n">
+        <v>25</v>
+      </c>
+      <c r="I48" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>ambiental</t>
+          <t>poesia e ensaio</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>114</v>
+        <v>3</v>
       </c>
       <c r="C49" t="n">
-        <v>346</v>
+        <v>72</v>
       </c>
       <c r="D49" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E49" t="n">
-        <v>46</v>
+        <v>696</v>
+      </c>
+      <c r="F49" t="n">
+        <v>36</v>
+      </c>
+      <c r="G49" t="n">
+        <v>20</v>
+      </c>
+      <c r="H49" t="n">
+        <v>26</v>
+      </c>
+      <c r="I49" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="50">
@@ -1374,35 +1970,59 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
         <v>41</v>
       </c>
-      <c r="D50" t="n">
-        <v>19</v>
-      </c>
-      <c r="E50" t="n">
-        <v>47</v>
+      <c r="F50" t="n">
+        <v>11</v>
+      </c>
+      <c r="G50" t="n">
+        <v>8</v>
+      </c>
+      <c r="H50" t="n">
+        <v>23</v>
+      </c>
+      <c r="I50" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>poesia e ensaio</t>
+          <t>saúde mental</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>223</v>
+        <v>4</v>
       </c>
       <c r="C51" t="n">
-        <v>696</v>
+        <v>28</v>
       </c>
       <c r="D51" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="E51" t="n">
-        <v>50</v>
+        <v>284</v>
+      </c>
+      <c r="F51" t="n">
+        <v>13</v>
+      </c>
+      <c r="G51" t="n">
+        <v>24</v>
+      </c>
+      <c r="H51" t="n">
+        <v>13</v>
+      </c>
+      <c r="I51" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="52">
@@ -1412,16 +2032,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C52" t="n">
+        <v>6</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" t="n">
         <v>41</v>
       </c>
-      <c r="D52" t="n">
-        <v>24</v>
-      </c>
-      <c r="E52" t="n">
-        <v>61</v>
+      <c r="F52" t="n">
+        <v>7</v>
+      </c>
+      <c r="G52" t="n">
+        <v>17</v>
+      </c>
+      <c r="H52" t="n">
+        <v>28</v>
+      </c>
+      <c r="I52" t="n">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
